--- a/data/trans_camb/IP26C_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 6,22</t>
+          <t>-9,64; 6,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 4,52</t>
+          <t>-12,44; 4,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 2,46</t>
+          <t>-13,18; 3,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 17,83</t>
+          <t>2,08; 18,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 7,52</t>
+          <t>-5,73; 7,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 16,94</t>
+          <t>-1,32; 17,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 9,98</t>
+          <t>-1,83; 9,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 3,45</t>
+          <t>-6,65; 3,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 7,98</t>
+          <t>-5,29; 7,24</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,15; 67,74</t>
+          <t>-56,23; 66,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-75,19; 46,44</t>
+          <t>-72,85; 50,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,42; 36,86</t>
+          <t>-78,2; 47,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,46; 440,51</t>
+          <t>15,47; 513,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,03; 215,13</t>
+          <t>-65,13; 197,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 399,99</t>
+          <t>-17,79; 426,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 131,78</t>
+          <t>-14,93; 123,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,75; 48,09</t>
+          <t>-56,15; 47,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-44,33; 97,33</t>
+          <t>-43,6; 91,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 3,23</t>
+          <t>-3,75; 3,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 1,28</t>
+          <t>-5,16; 1,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 1,34</t>
+          <t>-5,57; 1,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,49</t>
+          <t>-2,65; 3,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 2,96</t>
+          <t>-3,43; 3,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 3,74</t>
+          <t>-3,14; 3,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,45</t>
+          <t>-2,18; 2,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,21</t>
+          <t>-3,36; 1,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,64</t>
+          <t>-2,94; 1,67</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 33,67</t>
+          <t>-28,71; 35,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 13,93</t>
+          <t>-39,26; 18,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,35; 14,65</t>
+          <t>-42,39; 15,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 42,96</t>
+          <t>-23,03; 45,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 34,77</t>
+          <t>-30,0; 37,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 47,71</t>
+          <t>-28,05; 42,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 26,85</t>
+          <t>-18,46; 28,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,94; 13,31</t>
+          <t>-28,06; 11,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 16,62</t>
+          <t>-25,07; 18,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 1,25</t>
+          <t>-8,81; 1,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 3,74</t>
+          <t>-6,93; 3,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 2,3</t>
+          <t>-7,89; 2,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 5,24</t>
+          <t>-5,81; 5,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 3,71</t>
+          <t>-6,17; 4,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 7,05</t>
+          <t>-3,56; 7,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 1,74</t>
+          <t>-5,59; 1,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 2,78</t>
+          <t>-4,91; 2,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 3,06</t>
+          <t>-4,25; 3,46</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,78; 19,01</t>
+          <t>-65,25; 16,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,21; 43,83</t>
+          <t>-50,84; 43,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,39; 25,74</t>
+          <t>-57,68; 37,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,55; 76,76</t>
+          <t>-44,85; 76,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,59; 53,94</t>
+          <t>-47,72; 56,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 90,58</t>
+          <t>-30,78; 105,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,06; 19,57</t>
+          <t>-45,64; 25,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 31,9</t>
+          <t>-40,04; 30,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 34,43</t>
+          <t>-32,88; 41,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,46</t>
+          <t>-3,89; 1,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,3</t>
+          <t>-5,03; 0,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,46; -0,08</t>
+          <t>-5,29; 0,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,9</t>
+          <t>-0,97; 4,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,21</t>
+          <t>-2,81; 2,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,33</t>
+          <t>-1,35; 4,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,99</t>
+          <t>-1,67; 2,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,64</t>
+          <t>-2,93; 0,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,36</t>
+          <t>-2,4; 1,66</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 14,37</t>
+          <t>-29,57; 13,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 3,48</t>
+          <t>-38,31; 3,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 0,23</t>
+          <t>-40,38; 2,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 45,86</t>
+          <t>-9,45; 52,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 27,13</t>
+          <t>-25,62; 27,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 52,48</t>
+          <t>-12,65; 50,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 20,32</t>
+          <t>-14,84; 21,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,96; 6,65</t>
+          <t>-25,76; 5,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 13,98</t>
+          <t>-21,15; 17,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP26C_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 6,06</t>
+          <t>-10,03; 5,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 4,51</t>
+          <t>-13,04; 3,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 3,42</t>
+          <t>-13,63; 2,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 18,52</t>
+          <t>2,45; 17,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 7,82</t>
+          <t>-5,69; 8,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 17,41</t>
+          <t>-1,18; 17,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 9,86</t>
+          <t>-1,23; 9,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 3,38</t>
+          <t>-7,43; 3,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 7,24</t>
+          <t>-5,18; 7,25</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,23; 66,52</t>
+          <t>-59,41; 64,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,85; 50,45</t>
+          <t>-74,65; 37,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-78,2; 47,76</t>
+          <t>-81,43; 36,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,47; 513,79</t>
+          <t>14,68; 443,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,13; 197,72</t>
+          <t>-66,49; 230,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 426,88</t>
+          <t>-20,57; 413,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 123,65</t>
+          <t>-10,68; 123,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,15; 47,64</t>
+          <t>-59,6; 51,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 91,19</t>
+          <t>-44,12; 88,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 3,39</t>
+          <t>-3,64; 3,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 1,66</t>
+          <t>-5,43; 1,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 1,57</t>
+          <t>-5,54; 1,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 3,6</t>
+          <t>-2,87; 3,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 3,01</t>
+          <t>-3,38; 3,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,68</t>
+          <t>-3,14; 3,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 2,57</t>
+          <t>-2,05; 2,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,16</t>
+          <t>-3,17; 1,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,67</t>
+          <t>-3,04; 1,56</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 35,42</t>
+          <t>-28,83; 34,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,26; 18,42</t>
+          <t>-41,13; 12,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 15,77</t>
+          <t>-43,46; 14,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 45,51</t>
+          <t>-24,06; 41,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 37,58</t>
+          <t>-29,71; 38,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 42,51</t>
+          <t>-27,55; 43,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 28,23</t>
+          <t>-17,89; 31,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 11,79</t>
+          <t>-27,16; 13,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 18,15</t>
+          <t>-26,25; 16,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 1,28</t>
+          <t>-9,16; 1,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 3,85</t>
+          <t>-7,02; 4,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 2,85</t>
+          <t>-8,06; 2,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 5,4</t>
+          <t>-5,53; 5,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 4,07</t>
+          <t>-6,23; 4,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 7,68</t>
+          <t>-4,21; 7,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 1,92</t>
+          <t>-5,51; 1,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,63</t>
+          <t>-4,85; 2,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 3,46</t>
+          <t>-4,0; 3,82</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,25; 16,0</t>
+          <t>-65,37; 19,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 43,75</t>
+          <t>-49,29; 53,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,68; 37,23</t>
+          <t>-58,65; 27,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,85; 76,44</t>
+          <t>-42,7; 84,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,72; 56,05</t>
+          <t>-48,59; 70,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 105,62</t>
+          <t>-32,9; 105,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,64; 25,27</t>
+          <t>-45,53; 20,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 30,47</t>
+          <t>-39,15; 27,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 41,56</t>
+          <t>-32,84; 44,41</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 1,39</t>
+          <t>-3,71; 1,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,35</t>
+          <t>-5,14; 0,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 0,22</t>
+          <t>-5,06; 0,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,08</t>
+          <t>-1,25; 4,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,26</t>
+          <t>-2,69; 2,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 4,23</t>
+          <t>-1,47; 4,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,14</t>
+          <t>-1,57; 2,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,56</t>
+          <t>-3,07; 0,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,66</t>
+          <t>-2,6; 1,4</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 13,56</t>
+          <t>-29,2; 15,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 3,7</t>
+          <t>-39,1; 4,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,38; 2,97</t>
+          <t>-40,59; 4,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 52,76</t>
+          <t>-12,03; 48,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 27,38</t>
+          <t>-25,03; 26,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 50,23</t>
+          <t>-14,06; 50,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 21,89</t>
+          <t>-13,78; 21,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 5,92</t>
+          <t>-25,86; 5,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 17,59</t>
+          <t>-22,73; 13,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP26C_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10,1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,65</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,92</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,57</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-4,81</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,92</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,44</t>
+          <t>-4,2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>2,58</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 5,93</t>
+          <t>2,47; 17,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 3,57</t>
+          <t>-5,68; 7,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 2,72</t>
+          <t>-0,36; 19,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 17,78</t>
+          <t>-9,64; 6,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 8,16</t>
+          <t>-13,35; 4,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 17,33</t>
+          <t>-12,4; 5,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 9,67</t>
+          <t>-1,59; 9,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 3,4</t>
+          <t>-7,14; 3,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 7,25</t>
+          <t>-3,74; 10,23</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>150,12%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>132,59%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-11,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-35,67%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-43,94%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>150,12%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>110,61%</t>
+          <t>-31,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,41; 64,38</t>
+          <t>13,46; 440,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,65; 37,82</t>
+          <t>-66,03; 215,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,43; 36,99</t>
+          <t>-14,82; 455,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,68; 443,5</t>
+          <t>-54,15; 67,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,49; 230,29</t>
+          <t>-75,19; 46,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 413,02</t>
+          <t>-74,44; 67,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 123,52</t>
+          <t>-11,48; 131,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,6; 51,52</t>
+          <t>-57,75; 48,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 88,17</t>
+          <t>-32,62; 135,53</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,42</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,22</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-2,0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,04</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 3,26</t>
+          <t>-2,56; 3,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 1,3</t>
+          <t>-3,51; 2,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 1,38</t>
+          <t>-2,54; 4,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 3,4</t>
+          <t>-3,87; 3,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,16</t>
+          <t>-5,06; 1,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,57</t>
+          <t>-4,57; 2,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,87</t>
+          <t>-2,27; 2,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,18</t>
+          <t>-3,34; 1,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,56</t>
+          <t>-2,72; 2,03</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-0,94%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-1,94%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-17,42%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-17,83%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-0,94%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>-11,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-7,05%</t>
+          <t>-2,3%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,83; 34,73</t>
+          <t>-23,12; 42,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,13; 12,84</t>
+          <t>-30,29; 34,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 14,65</t>
+          <t>-22,92; 49,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 41,92</t>
+          <t>-29,47; 33,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 38,68</t>
+          <t>-37,84; 13,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,55; 43,32</t>
+          <t>-34,72; 23,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 31,43</t>
+          <t>-19,13; 26,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 13,17</t>
+          <t>-27,94; 13,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 16,4</t>
+          <t>-23,93; 21,16</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,95</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,07</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-3,75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,54</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,73</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>-2,38</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 1,58</t>
+          <t>-5,65; 5,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 4,03</t>
+          <t>-6,43; 3,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 2,14</t>
+          <t>-4,18; 7,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 5,68</t>
+          <t>-8,9; 1,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 4,4</t>
+          <t>-6,93; 3,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 7,48</t>
+          <t>-7,66; 2,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 1,83</t>
+          <t>-5,57; 1,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 2,33</t>
+          <t>-5,03; 2,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 3,82</t>
+          <t>-3,85; 3,66</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-9,49%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20,66%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-34,09%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-13,95%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-24,8%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-9,49%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>-21,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-3,09%</t>
+          <t>-0,75%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,37; 19,95</t>
+          <t>-43,55; 76,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-49,29; 53,33</t>
+          <t>-48,59; 53,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,65; 27,72</t>
+          <t>-34,5; 94,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,7; 84,4</t>
+          <t>-65,78; 19,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,59; 70,7</t>
+          <t>-51,21; 43,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,9; 105,98</t>
+          <t>-56,84; 31,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,53; 20,11</t>
+          <t>-45,06; 19,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,15; 27,81</t>
+          <t>-39,69; 31,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,84; 44,41</t>
+          <t>-30,7; 40,75</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,21</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,22</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,61</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,43</t>
+          <t>-1,93</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,52</t>
+          <t>-1,17; 3,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,45</t>
+          <t>-2,62; 2,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 0,41</t>
+          <t>-0,88; 4,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,15</t>
+          <t>-3,92; 1,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,23</t>
+          <t>-4,95; 0,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,11</t>
+          <t>-4,72; 0,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,08</t>
+          <t>-1,64; 1,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,5</t>
+          <t>-2,97; 0,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,4</t>
+          <t>-1,81; 1,93</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>15,64%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-1,57%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19,6%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-10,45%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-19,08%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-22,46%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>15,64%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-1,57%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>-16,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-4,73%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 15,52</t>
+          <t>-11,18; 45,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 4,48</t>
+          <t>-24,66; 27,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,59; 4,68</t>
+          <t>-8,04; 57,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 48,99</t>
+          <t>-30,1; 14,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 26,49</t>
+          <t>-38,25; 3,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 50,15</t>
+          <t>-35,98; 8,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 21,63</t>
+          <t>-14,4; 20,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,86; 5,32</t>
+          <t>-25,96; 6,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,73; 13,85</t>
+          <t>-15,87; 19,62</t>
         </is>
       </c>
     </row>
